--- a/data/trans_dic/P45C_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R2-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,83; 19,4</t>
+          <t>13,78; 19,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,96; 20,65</t>
+          <t>15,24; 20,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 10,73</t>
+          <t>6,06; 10,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,96; 26,63</t>
+          <t>17,92; 26,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,46; 11,73</t>
+          <t>7,42; 11,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,95; 16,73</t>
+          <t>11,01; 16,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,88; 10,0</t>
+          <t>5,92; 9,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,69; 19,6</t>
+          <t>14,75; 19,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,09; 14,76</t>
+          <t>11,26; 14,89</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,77; 17,8</t>
+          <t>13,86; 17,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,45; 9,3</t>
+          <t>6,53; 9,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,13; 22,16</t>
+          <t>16,85; 21,83</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,17; 19,23</t>
+          <t>14,2; 19,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,75; 18,67</t>
+          <t>13,8; 18,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,98; 15,38</t>
+          <t>10,87; 15,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 15,43</t>
+          <t>5,72; 15,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,7; 13,96</t>
+          <t>9,7; 13,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,81; 15,11</t>
+          <t>10,88; 14,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,17; 14,26</t>
+          <t>10,3; 14,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,93; 17,12</t>
+          <t>12,91; 17,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,65; 15,87</t>
+          <t>12,62; 15,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,87; 15,94</t>
+          <t>12,82; 16,1</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,99; 14,07</t>
+          <t>10,95; 14,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,06; 15,23</t>
+          <t>8,74; 15,3</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,08; 17,58</t>
+          <t>12,03; 17,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,39; 21,2</t>
+          <t>15,11; 21,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,98; 18,39</t>
+          <t>13,06; 18,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,97; 22,16</t>
+          <t>14,66; 22,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,18; 17,4</t>
+          <t>12,04; 17,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,72; 16,99</t>
+          <t>11,83; 16,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,5; 21,07</t>
+          <t>15,21; 21,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,71; 13,32</t>
+          <t>4,85; 13,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,71; 16,39</t>
+          <t>12,79; 16,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,28; 18,1</t>
+          <t>14,22; 18,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,9; 18,86</t>
+          <t>15,04; 18,89</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,22; 16,41</t>
+          <t>8,49; 16,29</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,96; 17,32</t>
+          <t>12,94; 17,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,21; 21,55</t>
+          <t>16,37; 21,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,08; 18,77</t>
+          <t>13,97; 18,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,75; 16,91</t>
+          <t>11,61; 16,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,82; 16,05</t>
+          <t>11,72; 15,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,56; 15,8</t>
+          <t>11,65; 15,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,25; 17,78</t>
+          <t>13,24; 17,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,18; 11,31</t>
+          <t>7,32; 11,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,87; 15,97</t>
+          <t>12,86; 15,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,44; 17,62</t>
+          <t>14,37; 17,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,21; 17,37</t>
+          <t>14,18; 17,55</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,76; 13,14</t>
+          <t>9,73; 12,95</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,4; 16,93</t>
+          <t>14,42; 17,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,3; 18,91</t>
+          <t>16,22; 18,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,39; 14,88</t>
+          <t>12,22; 14,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,39; 17,27</t>
+          <t>12,05; 17,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,29; 13,53</t>
+          <t>11,4; 13,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,23; 14,66</t>
+          <t>12,26; 14,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,43; 14,69</t>
+          <t>12,39; 14,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,16; 13,69</t>
+          <t>10,05; 13,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,16; 14,92</t>
+          <t>13,15; 14,93</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,67; 16,4</t>
+          <t>14,62; 16,41</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,65; 14,43</t>
+          <t>12,73; 14,33</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,04; 15,0</t>
+          <t>11,95; 15,06</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>95808; 134426</t>
+          <t>95488; 135720</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>104366; 144081</t>
+          <t>106344; 146377</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41204; 72199</t>
+          <t>40767; 69399</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113463; 168211</t>
+          <t>113177; 170391</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>51367; 80777</t>
+          <t>51105; 79580</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76114; 116293</t>
+          <t>76489; 112884</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39412; 66986</t>
+          <t>39638; 66906</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>99155; 132285</t>
+          <t>99546; 130876</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>153230; 203861</t>
+          <t>155521; 205673</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>191732; 247963</t>
+          <t>192982; 246842</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>86668; 124880</t>
+          <t>87624; 126653</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>223742; 289497</t>
+          <t>220158; 285178</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>135778; 184281</t>
+          <t>136111; 185156</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>138637; 188197</t>
+          <t>139162; 183755</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>111159; 155785</t>
+          <t>110065; 157054</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>69804; 183901</t>
+          <t>68138; 186489</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>93623; 134694</t>
+          <t>93570; 133094</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>110344; 154326</t>
+          <t>111152; 151708</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>105443; 147807</t>
+          <t>106762; 148778</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>123811; 163870</t>
+          <t>123589; 164503</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>243335; 305192</t>
+          <t>242781; 303195</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>261074; 323447</t>
+          <t>260209; 326616</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>225285; 288282</t>
+          <t>224303; 287786</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>194653; 327356</t>
+          <t>187810; 328787</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>81865; 119121</t>
+          <t>81516; 119709</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>115328; 158882</t>
+          <t>113218; 157457</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97212; 137734</t>
+          <t>97814; 138827</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>105120; 155644</t>
+          <t>102936; 156120</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>83092; 118718</t>
+          <t>82103; 117282</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>89992; 130385</t>
+          <t>90818; 130259</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>120184; 163382</t>
+          <t>117966; 164689</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43928; 124246</t>
+          <t>45214; 127895</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>172826; 222837</t>
+          <t>173977; 226524</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>216624; 274555</t>
+          <t>215745; 274204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>227102; 287625</t>
+          <t>229303; 288005</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>134393; 268358</t>
+          <t>138842; 266283</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>121824; 162700</t>
+          <t>121578; 162578</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>153024; 203352</t>
+          <t>154488; 204200</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>131010; 174711</t>
+          <t>130020; 176210</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>108916; 156715</t>
+          <t>107634; 155128</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>122388; 166239</t>
+          <t>121332; 165025</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>120160; 164272</t>
+          <t>121094; 164524</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>137279; 184232</t>
+          <t>137252; 182085</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>78558; 123761</t>
+          <t>80122; 123775</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>254258; 315365</t>
+          <t>253968; 315810</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>286358; 349594</t>
+          <t>284993; 348694</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>279454; 341746</t>
+          <t>278853; 345181</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>197357; 265548</t>
+          <t>196681; 261732</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>470835; 553488</t>
+          <t>471293; 558570</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>553901; 642646</t>
+          <t>551193; 641753</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>417035; 500918</t>
+          <t>411298; 496714</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>427918; 596289</t>
+          <t>415959; 602016</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>380482; 456084</t>
+          <t>384174; 457603</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>430882; 516401</t>
+          <t>431953; 515392</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>437175; 516935</t>
+          <t>436026; 517030</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>371769; 501114</t>
+          <t>367559; 499047</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>873613; 990516</t>
+          <t>873195; 991115</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1015275; 1135391</t>
+          <t>1012265; 1136203</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>870594; 993009</t>
+          <t>876401; 986589</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>856184; 1066815</t>
+          <t>850031; 1071214</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P45C_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P45C_R2-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,78; 19,58</t>
+          <t>13,55; 19,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,24; 20,98</t>
+          <t>15,04; 20,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6,06; 10,31</t>
+          <t>6,1; 10,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,92; 26,97</t>
+          <t>18,21; 25,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,42; 11,56</t>
+          <t>7,5; 11,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,01; 16,24</t>
+          <t>10,91; 16,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 9,99</t>
+          <t>5,85; 9,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14,75; 19,39</t>
+          <t>14,28; 18,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,26; 14,89</t>
+          <t>11,33; 14,59</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13,86; 17,72</t>
+          <t>13,92; 17,87</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,53; 9,43</t>
+          <t>6,54; 9,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,85; 21,83</t>
+          <t>16,94; 21,36</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,2; 19,32</t>
+          <t>14,27; 19,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,8; 18,23</t>
+          <t>13,68; 18,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,87; 15,51</t>
+          <t>10,78; 15,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 15,65</t>
+          <t>12,56; 17,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,7; 13,79</t>
+          <t>9,78; 14,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,88; 14,86</t>
+          <t>10,82; 15,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,3; 14,36</t>
+          <t>10,21; 14,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,91; 17,18</t>
+          <t>12,85; 16,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,62; 15,76</t>
+          <t>12,55; 15,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,82; 16,1</t>
+          <t>12,84; 16,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,95; 14,05</t>
+          <t>11,21; 14,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,74; 15,3</t>
+          <t>13,17; 16,56</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,03; 17,66</t>
+          <t>11,85; 17,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,11; 21,01</t>
+          <t>15,47; 21,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,06; 18,53</t>
+          <t>13,01; 18,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,66; 22,23</t>
+          <t>15,33; 22,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,04; 17,19</t>
+          <t>11,95; 17,26</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,83; 16,97</t>
+          <t>11,54; 16,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,21; 21,24</t>
+          <t>15,46; 21,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,85; 13,71</t>
+          <t>11,33; 16,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,79; 16,66</t>
+          <t>12,69; 16,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,22; 18,08</t>
+          <t>14,42; 18,29</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,04; 18,89</t>
+          <t>14,96; 19,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8,49; 16,29</t>
+          <t>13,96; 18,0</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,94; 17,3</t>
+          <t>12,96; 17,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,37; 21,63</t>
+          <t>16,59; 21,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,97; 18,93</t>
+          <t>13,78; 18,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,61; 16,74</t>
+          <t>12,24; 17,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,72; 15,94</t>
+          <t>11,68; 16,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,65; 15,82</t>
+          <t>11,41; 15,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,24; 17,57</t>
+          <t>13,23; 17,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 11,31</t>
+          <t>8,21; 11,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,86; 15,99</t>
+          <t>12,89; 15,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,37; 17,58</t>
+          <t>14,4; 17,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14,18; 17,55</t>
+          <t>14,22; 17,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,73; 12,95</t>
+          <t>10,56; 13,66</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,42; 17,09</t>
+          <t>14,45; 17,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,22; 18,88</t>
+          <t>16,22; 18,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12,22; 14,76</t>
+          <t>12,24; 14,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,05; 17,44</t>
+          <t>15,51; 18,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,4; 13,57</t>
+          <t>11,29; 13,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,26; 14,63</t>
+          <t>12,43; 14,68</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,39; 14,7</t>
+          <t>12,43; 14,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,05; 13,64</t>
+          <t>12,32; 14,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,15; 14,93</t>
+          <t>13,26; 14,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,62; 16,41</t>
+          <t>14,62; 16,35</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,73; 14,33</t>
+          <t>12,73; 14,4</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,95; 15,06</t>
+          <t>14,26; 16,07</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>136892</t>
+          <t>147823</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>114482</t>
+          <t>121905</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>251375</t>
+          <t>269728</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>95488; 135720</t>
+          <t>93927; 134429</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>106344; 146377</t>
+          <t>104932; 146482</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40767; 69399</t>
+          <t>41061; 72002</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>113177; 170391</t>
+          <t>125101; 174959</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>51105; 79580</t>
+          <t>51660; 80637</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76489; 112884</t>
+          <t>75823; 113719</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39638; 66906</t>
+          <t>39214; 65731</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>99546; 130876</t>
+          <t>104510; 138931</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>155521; 205673</t>
+          <t>156553; 201573</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>192982; 246842</t>
+          <t>193852; 248952</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>87624; 126653</t>
+          <t>87816; 126290</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>220158; 285178</t>
+          <t>240335; 303117</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>137250</t>
+          <t>158575</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>142352</t>
+          <t>155962</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>279602</t>
+          <t>314537</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>136111; 185156</t>
+          <t>136805; 183741</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>139162; 183755</t>
+          <t>137876; 185650</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>110065; 157054</t>
+          <t>109197; 156503</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>68138; 186489</t>
+          <t>131610; 187540</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>93570; 133094</t>
+          <t>94368; 135083</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>111152; 151708</t>
+          <t>110517; 154543</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>106762; 148778</t>
+          <t>105776; 148978</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>123589; 164503</t>
+          <t>137457; 177562</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>242781; 303195</t>
+          <t>241399; 301688</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>260209; 326616</t>
+          <t>260592; 324997</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>224303; 287786</t>
+          <t>229794; 290767</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>187810; 328787</t>
+          <t>278828; 350642</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128663</t>
+          <t>148408</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>92016</t>
+          <t>108276</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>220679</t>
+          <t>256684</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>81516; 119709</t>
+          <t>80283; 118539</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>113218; 157457</t>
+          <t>115940; 160565</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>97814; 138827</t>
+          <t>97447; 138063</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102936; 156120</t>
+          <t>122724; 176687</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>82103; 117282</t>
+          <t>81491; 117730</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>90818; 130259</t>
+          <t>88588; 127198</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>117966; 164689</t>
+          <t>119922; 164990</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>45214; 127895</t>
+          <t>91783; 129840</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>173977; 226524</t>
+          <t>172578; 223798</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>215745; 274204</t>
+          <t>218708; 277382</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>229303; 288005</t>
+          <t>228131; 290011</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>138842; 266283</t>
+          <t>224804; 289902</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>129211</t>
+          <t>143393</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>101593</t>
+          <t>111245</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>230803</t>
+          <t>254638</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>121578; 162578</t>
+          <t>121814; 162588</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>154488; 204200</t>
+          <t>156578; 203079</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>130020; 176210</t>
+          <t>128221; 172365</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>107634; 155128</t>
+          <t>121159; 170212</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>121332; 165025</t>
+          <t>120998; 167445</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>121094; 164524</t>
+          <t>118581; 163553</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>137252; 182085</t>
+          <t>137131; 185223</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>80122; 123775</t>
+          <t>91854; 133173</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>253968; 315810</t>
+          <t>254521; 315643</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>284993; 348694</t>
+          <t>285561; 350179</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>278853; 345181</t>
+          <t>279603; 343059</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>196681; 261732</t>
+          <t>222697; 287913</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>532017</t>
+          <t>598199</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>450443</t>
+          <t>497389</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>982460</t>
+          <t>1095588</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>471293; 558570</t>
+          <t>472239; 557285</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>551193; 641753</t>
+          <t>551494; 643560</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>411298; 496714</t>
+          <t>411999; 493086</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>415959; 602016</t>
+          <t>546737; 656550</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>384174; 457603</t>
+          <t>380718; 459893</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>431953; 515392</t>
+          <t>438102; 517413</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>436026; 517030</t>
+          <t>437319; 520957</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>367559; 499047</t>
+          <t>459725; 538703</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>873195; 991115</t>
+          <t>880119; 988972</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1012265; 1136203</t>
+          <t>1012196; 1131831</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>876401; 986589</t>
+          <t>876199; 990913</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>850031; 1071214</t>
+          <t>1034481; 1166270</t>
         </is>
       </c>
     </row>
